--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N81_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N81_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.884485677838851</v>
+        <v>0.9562289226488132</v>
       </c>
       <c r="D2" t="n">
-        <v>6.283386326363904</v>
+        <v>1.021050278034134</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
